--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -603,9 +603,14 @@
       <c r="E2" s="4" t="n">
         <v>46252.10625</v>
       </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1068217615798431</t>
         </is>
       </c>
     </row>
@@ -631,9 +636,14 @@
       <c r="E3" s="4" t="n">
         <v>46252.23125</v>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1742297390429502</t>
         </is>
       </c>
     </row>
@@ -659,9 +669,14 @@
       <c r="E4" s="4" t="n">
         <v>46252.73125</v>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2258655078323724</t>
         </is>
       </c>
     </row>
@@ -687,9 +702,14 @@
       <c r="E5" s="4" t="n">
         <v>46252.85625</v>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2142237863001000</t>
         </is>
       </c>
     </row>
@@ -715,9 +735,14 @@
       <c r="E6" s="4" t="n">
         <v>46252.98125</v>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4692523567652131</t>
         </is>
       </c>
     </row>
@@ -743,9 +768,14 @@
       <c r="E7" s="4" t="n">
         <v>46253.10625</v>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1039727018945929</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\All Auto Post\Pets Swag - Monk K\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248FB8D0-BFD7-40E8-928C-3BECE9A11DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B7ACE5-D83E-4C83-9AC2-C4D766F23563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CEBFA179-F109-4830-AF10-F3EF48EB9847}"/>
   </bookViews>
@@ -4948,7 +4948,7 @@
         <v>82</v>
       </c>
       <c r="E174" s="4">
-        <v>46289.522916666669</v>
+        <v>46258.526388888888</v>
       </c>
       <c r="F174" s="5" t="s">
         <v>8</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -755,9 +755,14 @@
       <c r="E7" s="4" t="n">
         <v>46259.73125</v>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1727501888470066</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -788,9 +788,14 @@
       <c r="E8" s="4" t="n">
         <v>46259.85625</v>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1844335123205088</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -881,9 +881,14 @@
       <c r="E11" s="4" t="n">
         <v>46260.23125</v>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1058782020381431</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\All Auto Post\Pets Swag - Monk K\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sanuk\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E73557C-A328-4D4C-A077-EB5FE48C557C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C97626D0-2278-4623-9522-68796305563B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1070,7 +1070,7 @@
     <col min="5" max="5" width="29" customWidth="1"/>
     <col min="6" max="6" width="23.42578125" customWidth="1"/>
     <col min="7" max="7" width="30.85546875" customWidth="1"/>
-    <col min="8" max="8" width="23.140625" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1405,7 +1405,7 @@
         <v>29</v>
       </c>
       <c r="E16" s="4">
-        <v>46261.558333333334</v>
+        <v>46294.981249999997</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>10</v>
@@ -1425,7 +1425,7 @@
         <v>30</v>
       </c>
       <c r="E17" s="4">
-        <v>46261.731249999997</v>
+        <v>46295.106249999997</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>10</v>
@@ -1445,7 +1445,7 @@
         <v>31</v>
       </c>
       <c r="E18" s="4">
-        <v>46261.856249999997</v>
+        <v>46295.231249999997</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>10</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1153,9 +1153,14 @@
       <c r="E20" s="4" t="n">
         <v>46262.10625</v>
       </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2276412926525506</t>
         </is>
       </c>
     </row>
@@ -1181,9 +1186,14 @@
       <c r="E21" s="4" t="n">
         <v>46262.23125</v>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2086245928947302</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1322,9 +1322,14 @@
       <c r="E25" s="4" t="n">
         <v>46263.10625</v>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>900598909483032</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1355,9 +1355,14 @@
       <c r="E26" s="4" t="n">
         <v>46263.23125</v>
       </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1018874884466903</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1388,9 +1388,14 @@
       <c r="E27" s="4" t="n">
         <v>46263.73125</v>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1446639020853798</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1421,9 +1421,14 @@
       <c r="E28" s="4" t="n">
         <v>46263.85625</v>
       </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1560622415055816</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1454,9 +1454,14 @@
       <c r="E29" s="4" t="n">
         <v>46263.98125</v>
       </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>27993899946971684</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1487,9 +1487,14 @@
       <c r="E30" s="4" t="n">
         <v>46264.10625</v>
       </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>4064145463722958</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1520,9 +1520,14 @@
       <c r="E31" s="4" t="n">
         <v>46264.23125</v>
       </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>3105609382961323</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1553,9 +1553,14 @@
       <c r="E32" s="4" t="n">
         <v>46264.73125</v>
       </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2237416860368487</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1586,9 +1586,14 @@
       <c r="E33" s="4" t="n">
         <v>46264.85625</v>
       </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2688978428187867</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1619,9 +1619,14 @@
       <c r="E34" s="4" t="n">
         <v>46264.98125</v>
       </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>3144505225740313</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1652,9 +1652,14 @@
       <c r="E35" s="4" t="n">
         <v>46265.10625</v>
       </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>4035609929902801</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1685,9 +1685,14 @@
       <c r="E36" s="4" t="n">
         <v>46265.23125</v>
       </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>927810873730289</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1718,9 +1718,14 @@
       <c r="E37" s="4" t="n">
         <v>46265.73125</v>
       </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1089313166933027</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1751,9 +1751,14 @@
       <c r="E38" s="4" t="n">
         <v>46265.85625</v>
       </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>4569840709926287</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1784,9 +1784,14 @@
       <c r="E39" s="4" t="n">
         <v>46265.98125</v>
       </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>933242939260153</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1817,9 +1817,14 @@
       <c r="E40" s="4" t="n">
         <v>46266.10625</v>
       </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>896840996549118</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1850,9 +1850,14 @@
       <c r="E41" s="4" t="n">
         <v>46266.23125</v>
       </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1600092194828421</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1883,9 +1883,14 @@
       <c r="E42" s="4" t="n">
         <v>46266.73125</v>
       </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1432378472117750</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1916,9 +1916,14 @@
       <c r="E43" s="4" t="n">
         <v>46266.85625</v>
       </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1749115812965474</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1949,9 +1949,14 @@
       <c r="E44" s="4" t="n">
         <v>46266.98125</v>
       </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1071353192108789</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1982,9 +1982,14 @@
       <c r="E45" s="4" t="n">
         <v>46267.10625</v>
       </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1375302177510230</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2015,9 +2015,14 @@
       <c r="E46" s="4" t="n">
         <v>46267.23125</v>
       </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1478928760730567</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2048,9 +2048,14 @@
       <c r="E47" s="4" t="n">
         <v>46267.73125</v>
       </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1708682017029130</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2081,9 +2081,14 @@
       <c r="E48" s="4" t="n">
         <v>46267.85625</v>
       </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1773294030541801</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2114,9 +2114,14 @@
       <c r="E49" s="4" t="n">
         <v>46267.98125</v>
       </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2086528215404416</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2147,9 +2147,14 @@
       <c r="E50" s="4" t="n">
         <v>46268.10625</v>
       </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1973070849855272</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2180,9 +2180,14 @@
       <c r="E51" s="4" t="n">
         <v>46268.23125</v>
       </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1868057410844667</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2213,9 +2213,14 @@
       <c r="E52" s="4" t="n">
         <v>46268.73125</v>
       </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2138580117032780</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2246,9 +2246,14 @@
       <c r="E53" s="4" t="n">
         <v>46268.85625</v>
       </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>874981272216992</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2279,9 +2279,14 @@
       <c r="E54" s="4" t="n">
         <v>46268.98125</v>
       </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1363419429239074</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2312,9 +2312,14 @@
       <c r="E55" s="4" t="n">
         <v>46269.10625</v>
       </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1010599035373062</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2345,9 +2345,14 @@
       <c r="E56" s="4" t="n">
         <v>46269.23125</v>
       </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1046341265062358</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2378,9 +2378,14 @@
       <c r="E57" s="4" t="n">
         <v>46269.73125</v>
       </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1054766710495088</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2411,9 +2411,14 @@
       <c r="E58" s="4" t="n">
         <v>46269.85625</v>
       </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1621543259406023</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2444,9 +2444,14 @@
       <c r="E59" s="4" t="n">
         <v>46269.98125</v>
       </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2185909001965916</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2477,9 +2477,14 @@
       <c r="E60" s="4" t="n">
         <v>46270.10625</v>
       </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1429872468957712</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2510,9 +2510,14 @@
       <c r="E61" s="4" t="n">
         <v>46270.23125</v>
       </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1940874733250512</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2543,9 +2543,14 @@
       <c r="E62" s="4" t="n">
         <v>46270.73125</v>
       </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>3081961278862108</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2576,9 +2576,14 @@
       <c r="E63" s="4" t="n">
         <v>46270.85625</v>
       </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1001104656275142</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2609,9 +2609,14 @@
       <c r="E64" s="4" t="n">
         <v>46270.98125</v>
       </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1048484411320832</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2642,9 +2642,14 @@
       <c r="E65" s="4" t="n">
         <v>46271.10625</v>
       </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>28786397387630558</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2675,9 +2675,14 @@
       <c r="E66" s="4" t="n">
         <v>46271.23125</v>
       </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1933542264233135</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2708,9 +2708,14 @@
       <c r="E67" s="4" t="n">
         <v>46271.73125</v>
       </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1327184099269302</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2741,9 +2741,14 @@
       <c r="E68" s="4" t="n">
         <v>46271.85625</v>
       </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1077141861366941</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2774,9 +2774,14 @@
       <c r="E69" s="4" t="n">
         <v>46271.98125</v>
       </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1436305285077902</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2807,9 +2807,14 @@
       <c r="E70" s="4" t="n">
         <v>46272.10625</v>
       </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>951233883973193</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2840,9 +2840,14 @@
       <c r="E71" s="4" t="n">
         <v>46272.23125</v>
       </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>3109849365889000</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2873,9 +2873,14 @@
       <c r="E72" s="4" t="n">
         <v>46272.73125</v>
       </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1448798150422418</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2906,9 +2906,14 @@
       <c r="E73" s="4" t="n">
         <v>46272.85625</v>
       </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1062765703028891</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2939,9 +2939,14 @@
       <c r="E74" s="4" t="n">
         <v>46272.98125</v>
       </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2289692635144210</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2972,9 +2972,14 @@
       <c r="E75" s="4" t="n">
         <v>46273.10625</v>
       </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1373140621150292</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3005,9 +3005,14 @@
       <c r="E76" s="4" t="n">
         <v>46273.23125</v>
       </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1264076453462288</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3038,9 +3038,14 @@
       <c r="E77" s="4" t="n">
         <v>46273.73125</v>
       </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2476002462894273</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3071,9 +3071,14 @@
       <c r="E78" s="4" t="n">
         <v>46273.85625</v>
       </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2555306334984207</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3104,9 +3104,14 @@
       <c r="E79" s="4" t="n">
         <v>46273.98125</v>
       </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1744476753486664</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3137,9 +3137,14 @@
       <c r="E80" s="4" t="n">
         <v>46274.10625</v>
       </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1053584170914035</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3170,9 +3170,14 @@
       <c r="E81" s="4" t="n">
         <v>46274.23125</v>
       </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>938689995382313</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3203,9 +3203,14 @@
       <c r="E82" s="4" t="n">
         <v>46274.73125</v>
       </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1084266264051258</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3236,9 +3236,14 @@
       <c r="E83" s="4" t="n">
         <v>46274.85625</v>
       </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1102577782456336</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3269,9 +3269,14 @@
       <c r="E84" s="4" t="n">
         <v>46274.98125</v>
       </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>1782711119408397</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3302,9 +3302,14 @@
       <c r="E85" s="4" t="n">
         <v>46275.10625</v>
       </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F85" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1589711355939233</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3335,9 +3335,14 @@
       <c r="E86" s="4" t="n">
         <v>46275.23125</v>
       </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1063943333117306</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3368,9 +3368,14 @@
       <c r="E87" s="4" t="n">
         <v>46275.73125</v>
       </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1071930075752073</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3401,9 +3401,14 @@
       <c r="E88" s="4" t="n">
         <v>46275.85625</v>
       </c>
-      <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1710487336728562</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3434,9 +3434,14 @@
       <c r="E89" s="4" t="n">
         <v>46275.98125</v>
       </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2012114656102056</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3467,9 +3467,14 @@
       <c r="E90" s="4" t="n">
         <v>46276.10625</v>
       </c>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1362679892282044</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3500,9 +3500,14 @@
       <c r="E91" s="4" t="n">
         <v>46276.23125</v>
       </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1846276856356437</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3533,9 +3533,14 @@
       <c r="E92" s="4" t="n">
         <v>46276.73125</v>
       </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1796749521670767</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3566,9 +3566,14 @@
       <c r="E93" s="4" t="n">
         <v>46276.85625</v>
       </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>1990108081697761</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3599,9 +3599,14 @@
       <c r="E94" s="4" t="n">
         <v>46276.98125</v>
       </c>
-      <c r="F94" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>1060473390076139</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3632,9 +3632,14 @@
       <c r="E95" s="4" t="n">
         <v>46277.10625</v>
       </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>4039603972841090</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3665,9 +3665,14 @@
       <c r="E96" s="4" t="n">
         <v>46277.23125</v>
       </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2138087827125347</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3698,9 +3698,14 @@
       <c r="E97" s="4" t="n">
         <v>46277.73125</v>
       </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2671582843294786</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3731,9 +3731,14 @@
       <c r="E98" s="4" t="n">
         <v>46277.85625</v>
       </c>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>940647125148340</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3764,9 +3764,14 @@
       <c r="E99" s="4" t="n">
         <v>46277.98125</v>
       </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1398836138353817</t>
         </is>
       </c>
     </row>
